--- a/registration_forms/045_mastermind_event_registration--registration_forms.xlsx
+++ b/registration_forms/045_mastermind_event_registration--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Job Title Other Other</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Job Title Other Other Description</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>Job Title Other Other Value</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -941,8 +941,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="43" customWidth="1" min="2" max="2"/>
-    <col width="43" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -970,12 +970,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_16,_'name':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 16, 'name': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_17,_'name':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 17, 'name': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_18,_'name':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 18, 'name': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_19,_'name':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 19, 'name': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
